--- a/data/outputs/n_r_5_n_NEW.xlsx
+++ b/data/outputs/n_r_5_n_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,34 +444,44 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>break_minutes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>h100</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>h125</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>h150</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>shabbat</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>break</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>h100</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>h125</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>h150</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1/9/22</t>
+          <t>01/09/2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -479,15 +489,19 @@
           <t>חמישי</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -497,41 +511,47 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>219/22</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+          <t>02/09/2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -541,45 +561,47 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11/9/22</t>
+          <t>05/09/2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ראשון</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>שני</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,45 +611,47 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12/9/22</t>
+          <t>06/09/2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>שני</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -637,45 +661,47 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13/9/22</t>
+          <t>09/09/2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -685,45 +711,47 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14/9/22</t>
+          <t>12/09/2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>שני</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -733,45 +761,47 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15/9/22</t>
+          <t>13/09/2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -781,45 +811,47 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16/9/22</t>
+          <t>14/09/2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -829,45 +861,47 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18/9/22</t>
+          <t>15/09/2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ראשון</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -877,45 +911,47 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19/9/22</t>
+          <t>16/09/2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>שני</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -925,45 +961,47 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20/9/22</t>
+          <t>18/09/2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>ראשון</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -973,41 +1011,47 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2119/22</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+          <t>19/09/2022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>שני</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1017,45 +1061,47 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22/9/22</t>
+          <t>20/09/2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1065,41 +1111,47 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23/9122</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+          <t>28/09/2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1109,45 +1161,47 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28/9/22</t>
+          <t>29/09/2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1157,45 +1211,47 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>29/9/22</t>
+          <t>30/09/2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>שעת</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1205,70 +1261,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>30/9/22</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>

--- a/data/outputs/n_r_5_n_NEW.xlsx
+++ b/data/outputs/n_r_5_n_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>break_minutes</t>
+          <t>break</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -470,11 +470,6 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>shabbat</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>break</t>
         </is>
       </c>
     </row>
@@ -489,19 +484,15 @@
           <t>חמישי</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -522,11 +513,6 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -539,19 +525,15 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -572,11 +554,6 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -589,19 +566,15 @@
           <t>שני</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -622,11 +595,6 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -639,19 +607,15 @@
           <t>שלישי</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -672,11 +636,6 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -689,19 +648,15 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -722,11 +677,6 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -739,19 +689,15 @@
           <t>שני</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -772,11 +718,6 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -789,19 +730,15 @@
           <t>שלישי</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -822,11 +759,6 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -839,19 +771,15 @@
           <t>רביעי</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -872,11 +800,6 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -889,19 +812,15 @@
           <t>חמישי</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -922,11 +841,6 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -939,19 +853,15 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -972,11 +882,6 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -989,19 +894,15 @@
           <t>ראשון</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1022,11 +923,6 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1039,19 +935,15 @@
           <t>שני</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1072,11 +964,6 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1089,19 +976,15 @@
           <t>שלישי</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1122,11 +1005,6 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1139,19 +1017,15 @@
           <t>רביעי</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1172,11 +1046,6 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1189,11 +1058,7 @@
           <t>חמישי</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>08:35</t>
@@ -1222,11 +1087,6 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1239,19 +1099,15 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>שעת</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1272,11 +1128,6 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
